--- a/common/iTraxx.xlsx
+++ b/common/iTraxx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://axisalternatives1-my.sharepoint.com/personal/f_jordan-stagiaire_axisalternatives_com/Documents/Bureau/github environnement/Valo/common/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{96DB490B-B1AB-4BB6-8FA4-D651AA2679AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C020A166-F41B-47DD-8F12-EBD877B0A265}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{96DB490B-B1AB-4BB6-8FA4-D651AA2679AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A0FCD9A-9DD9-43E1-8A1A-389C3242351D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{95947EA3-354B-49D6-96D3-3A072B9C6938}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{95947EA3-354B-49D6-96D3-3A072B9C6938}"/>
   </bookViews>
   <sheets>
     <sheet name="Chart1" sheetId="2" state="hidden" r:id="rId1"/>
@@ -23202,31 +23202,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AEDA5EE-7B8E-4153-ABC5-44D5848ABB21}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:J318"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" customWidth="1"/>
+    <col min="5" max="5" width="17.26953125" customWidth="1"/>
+    <col min="6" max="6" width="24.81640625" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" customWidth="1"/>
+    <col min="8" max="8" width="11.7265625" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" customWidth="1"/>
+    <col min="10" max="10" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -23234,7 +23234,7 @@
         <v>45412</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -23263,7 +23263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -23293,7 +23293,7 @@
       </c>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -23323,7 +23323,7 @@
       </c>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -23353,7 +23353,7 @@
       </c>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -23383,7 +23383,7 @@
       </c>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -23413,7 +23413,7 @@
       </c>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -23443,7 +23443,7 @@
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -23473,7 +23473,7 @@
       </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -23503,7 +23503,7 @@
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -23533,7 +23533,7 @@
       </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -23563,7 +23563,7 @@
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -23593,7 +23593,7 @@
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -23623,7 +23623,7 @@
       </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -23649,7 +23649,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -23678,7 +23678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -23707,7 +23707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -23736,7 +23736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -23765,7 +23765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -23794,7 +23794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -23823,7 +23823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -23852,7 +23852,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -23881,7 +23881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -23910,7 +23910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -23939,7 +23939,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -23968,7 +23968,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -23997,7 +23997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -24026,7 +24026,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>43</v>
       </c>
@@ -24055,7 +24055,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>43</v>
       </c>
@@ -24084,7 +24084,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>44</v>
       </c>
@@ -24113,7 +24113,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>44</v>
       </c>
@@ -24142,7 +24142,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -24171,7 +24171,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -24200,7 +24200,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -24229,7 +24229,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>45</v>
       </c>
@@ -24258,7 +24258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>46</v>
       </c>
@@ -24287,7 +24287,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -24316,7 +24316,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -24345,7 +24345,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -24374,7 +24374,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -24403,7 +24403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -24432,7 +24432,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -24461,7 +24461,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -24490,7 +24490,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -24519,7 +24519,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -24548,7 +24548,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -24577,7 +24577,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -24606,7 +24606,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -24635,7 +24635,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>50</v>
       </c>
@@ -24664,7 +24664,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>50</v>
       </c>
@@ -24693,7 +24693,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -24722,7 +24722,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>51</v>
       </c>
@@ -24751,7 +24751,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>51</v>
       </c>
@@ -24780,7 +24780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>52</v>
       </c>
@@ -24809,7 +24809,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>52</v>
       </c>
@@ -24838,7 +24838,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>52</v>
       </c>
@@ -24867,7 +24867,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>53</v>
       </c>
@@ -24896,7 +24896,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>53</v>
       </c>
@@ -24925,7 +24925,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>53</v>
       </c>
@@ -24954,7 +24954,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>55</v>
       </c>
@@ -24983,7 +24983,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>55</v>
       </c>
@@ -25012,7 +25012,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>55</v>
       </c>
@@ -25041,7 +25041,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>56</v>
       </c>
@@ -25070,7 +25070,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>56</v>
       </c>
@@ -25099,7 +25099,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>56</v>
       </c>
@@ -25128,7 +25128,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>57</v>
       </c>
@@ -25157,7 +25157,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>57</v>
       </c>
@@ -25186,7 +25186,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>57</v>
       </c>
@@ -25215,7 +25215,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>58</v>
       </c>
@@ -25244,7 +25244,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>58</v>
       </c>
@@ -25273,7 +25273,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>58</v>
       </c>
@@ -25302,7 +25302,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>59</v>
       </c>
@@ -25331,7 +25331,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>59</v>
       </c>
@@ -25360,7 +25360,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>59</v>
       </c>
@@ -25389,7 +25389,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>60</v>
       </c>
@@ -25418,7 +25418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>60</v>
       </c>
@@ -25447,7 +25447,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>60</v>
       </c>
@@ -25476,7 +25476,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>32</v>
       </c>
@@ -25505,7 +25505,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>32</v>
       </c>
@@ -25534,7 +25534,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>32</v>
       </c>
@@ -25563,7 +25563,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>61</v>
       </c>
@@ -25592,7 +25592,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>61</v>
       </c>
@@ -25621,7 +25621,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>61</v>
       </c>
@@ -25650,7 +25650,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>62</v>
       </c>
@@ -25679,7 +25679,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>62</v>
       </c>
@@ -25708,7 +25708,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>62</v>
       </c>
@@ -25737,7 +25737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>63</v>
       </c>
@@ -25766,7 +25766,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>63</v>
       </c>
@@ -25795,7 +25795,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>63</v>
       </c>
@@ -25824,7 +25824,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>64</v>
       </c>
@@ -25853,7 +25853,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>64</v>
       </c>
@@ -25882,7 +25882,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>64</v>
       </c>
@@ -25911,7 +25911,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>65</v>
       </c>
@@ -25940,7 +25940,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>65</v>
       </c>
@@ -25969,7 +25969,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>65</v>
       </c>
@@ -25998,7 +25998,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>66</v>
       </c>
@@ -26027,7 +26027,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>66</v>
       </c>
@@ -26056,7 +26056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>66</v>
       </c>
@@ -26085,7 +26085,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>67</v>
       </c>
@@ -26114,7 +26114,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>67</v>
       </c>
@@ -26143,7 +26143,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>67</v>
       </c>
@@ -26172,7 +26172,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>68</v>
       </c>
@@ -26201,7 +26201,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>68</v>
       </c>
@@ -26230,7 +26230,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>68</v>
       </c>
@@ -26259,7 +26259,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>69</v>
       </c>
@@ -26288,7 +26288,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>69</v>
       </c>
@@ -26317,7 +26317,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>69</v>
       </c>
@@ -26346,7 +26346,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>70</v>
       </c>
@@ -26375,7 +26375,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>70</v>
       </c>
@@ -26404,7 +26404,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>70</v>
       </c>
@@ -26433,7 +26433,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>71</v>
       </c>
@@ -26462,7 +26462,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>71</v>
       </c>
@@ -26491,7 +26491,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>71</v>
       </c>
@@ -26520,7 +26520,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>72</v>
       </c>
@@ -26549,7 +26549,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>72</v>
       </c>
@@ -26578,7 +26578,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>72</v>
       </c>
@@ -26607,7 +26607,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>73</v>
       </c>
@@ -26636,7 +26636,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>73</v>
       </c>
@@ -26665,7 +26665,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>73</v>
       </c>
@@ -26694,7 +26694,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>74</v>
       </c>
@@ -26723,7 +26723,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>74</v>
       </c>
@@ -26752,7 +26752,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>74</v>
       </c>
@@ -26781,7 +26781,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>75</v>
       </c>
@@ -26810,7 +26810,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>75</v>
       </c>
@@ -26839,7 +26839,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>75</v>
       </c>
@@ -26868,7 +26868,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>76</v>
       </c>
@@ -26897,7 +26897,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>76</v>
       </c>
@@ -26926,7 +26926,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>76</v>
       </c>
@@ -26955,7 +26955,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>77</v>
       </c>
@@ -26984,7 +26984,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>77</v>
       </c>
@@ -27013,7 +27013,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>77</v>
       </c>
@@ -27042,7 +27042,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>78</v>
       </c>
@@ -27071,7 +27071,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>78</v>
       </c>
@@ -27100,7 +27100,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>78</v>
       </c>
@@ -27129,7 +27129,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>79</v>
       </c>
@@ -27158,7 +27158,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>79</v>
       </c>
@@ -27187,7 +27187,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>79</v>
       </c>
@@ -27216,7 +27216,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>80</v>
       </c>
@@ -27245,7 +27245,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>80</v>
       </c>
@@ -27274,7 +27274,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>80</v>
       </c>
@@ -27303,7 +27303,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>81</v>
       </c>
@@ -27332,7 +27332,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>81</v>
       </c>
@@ -27361,7 +27361,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>81</v>
       </c>
@@ -27390,7 +27390,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>82</v>
       </c>
@@ -27419,7 +27419,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>82</v>
       </c>
@@ -27448,7 +27448,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>82</v>
       </c>
@@ -27477,7 +27477,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>31</v>
       </c>
@@ -27506,7 +27506,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>31</v>
       </c>
@@ -27535,7 +27535,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>31</v>
       </c>
@@ -27564,7 +27564,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>83</v>
       </c>
@@ -27593,7 +27593,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>83</v>
       </c>
@@ -27622,7 +27622,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>83</v>
       </c>
@@ -27651,7 +27651,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>84</v>
       </c>
@@ -27680,7 +27680,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>84</v>
       </c>
@@ -27709,7 +27709,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>84</v>
       </c>
@@ -27738,7 +27738,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>85</v>
       </c>
@@ -27767,7 +27767,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>85</v>
       </c>
@@ -27796,7 +27796,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>85</v>
       </c>
@@ -27825,7 +27825,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>86</v>
       </c>
@@ -27854,7 +27854,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>86</v>
       </c>
@@ -27883,7 +27883,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>86</v>
       </c>
@@ -27912,7 +27912,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>87</v>
       </c>
@@ -27941,7 +27941,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>87</v>
       </c>
@@ -27970,7 +27970,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>87</v>
       </c>
@@ -27999,7 +27999,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>88</v>
       </c>
@@ -28028,7 +28028,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>88</v>
       </c>
@@ -28057,7 +28057,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>88</v>
       </c>
@@ -28086,7 +28086,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>89</v>
       </c>
@@ -28115,7 +28115,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>89</v>
       </c>
@@ -28144,7 +28144,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>89</v>
       </c>
@@ -28173,7 +28173,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>90</v>
       </c>
@@ -28202,7 +28202,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>90</v>
       </c>
@@ -28231,7 +28231,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>90</v>
       </c>
@@ -28260,7 +28260,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>91</v>
       </c>
@@ -28289,7 +28289,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>91</v>
       </c>
@@ -28318,7 +28318,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>91</v>
       </c>
@@ -28347,7 +28347,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>92</v>
       </c>
@@ -28376,7 +28376,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>92</v>
       </c>
@@ -28405,7 +28405,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>92</v>
       </c>
@@ -28434,7 +28434,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>93</v>
       </c>
@@ -28463,7 +28463,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>93</v>
       </c>
@@ -28492,7 +28492,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>93</v>
       </c>
@@ -28521,7 +28521,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>94</v>
       </c>
@@ -28550,7 +28550,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>94</v>
       </c>
@@ -28579,7 +28579,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>94</v>
       </c>
@@ -28608,7 +28608,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>95</v>
       </c>
@@ -28637,7 +28637,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>95</v>
       </c>
@@ -28666,7 +28666,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>95</v>
       </c>
@@ -28695,7 +28695,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>96</v>
       </c>
@@ -28724,7 +28724,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>96</v>
       </c>
@@ -28753,7 +28753,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>96</v>
       </c>
@@ -28782,7 +28782,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>97</v>
       </c>
@@ -28811,7 +28811,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>97</v>
       </c>
@@ -28840,7 +28840,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>97</v>
       </c>
@@ -28869,7 +28869,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>98</v>
       </c>
@@ -28898,7 +28898,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>98</v>
       </c>
@@ -28927,7 +28927,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>98</v>
       </c>
@@ -28956,7 +28956,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>99</v>
       </c>
@@ -28985,7 +28985,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>99</v>
       </c>
@@ -29014,7 +29014,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>99</v>
       </c>
@@ -29043,7 +29043,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>100</v>
       </c>
@@ -29072,7 +29072,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>100</v>
       </c>
@@ -29101,7 +29101,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>100</v>
       </c>
@@ -29130,7 +29130,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>131</v>
       </c>
@@ -29159,7 +29159,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>131</v>
       </c>
@@ -29188,7 +29188,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>131</v>
       </c>
@@ -29217,7 +29217,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>101</v>
       </c>
@@ -29246,7 +29246,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>101</v>
       </c>
@@ -29275,7 +29275,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>101</v>
       </c>
@@ -29304,7 +29304,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>102</v>
       </c>
@@ -29333,7 +29333,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>102</v>
       </c>
@@ -29362,7 +29362,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>102</v>
       </c>
@@ -29391,7 +29391,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>103</v>
       </c>
@@ -29420,7 +29420,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>103</v>
       </c>
@@ -29449,7 +29449,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>103</v>
       </c>
@@ -29478,7 +29478,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>104</v>
       </c>
@@ -29507,7 +29507,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>104</v>
       </c>
@@ -29536,7 +29536,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>104</v>
       </c>
@@ -29565,7 +29565,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>105</v>
       </c>
@@ -29594,7 +29594,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>105</v>
       </c>
@@ -29623,7 +29623,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>105</v>
       </c>
@@ -29652,7 +29652,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>106</v>
       </c>
@@ -29681,7 +29681,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>106</v>
       </c>
@@ -29710,7 +29710,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>106</v>
       </c>
@@ -29739,7 +29739,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>132</v>
       </c>
@@ -29768,7 +29768,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>132</v>
       </c>
@@ -29797,7 +29797,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>132</v>
       </c>
@@ -29826,7 +29826,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>107</v>
       </c>
@@ -29855,7 +29855,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>107</v>
       </c>
@@ -29884,7 +29884,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>107</v>
       </c>
@@ -29913,7 +29913,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>133</v>
       </c>
@@ -29942,7 +29942,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>133</v>
       </c>
@@ -29971,7 +29971,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>133</v>
       </c>
@@ -30000,7 +30000,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>134</v>
       </c>
@@ -30029,7 +30029,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>134</v>
       </c>
@@ -30058,7 +30058,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>134</v>
       </c>
@@ -30087,7 +30087,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>108</v>
       </c>
@@ -30116,7 +30116,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>108</v>
       </c>
@@ -30145,7 +30145,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>108</v>
       </c>
@@ -30174,7 +30174,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>109</v>
       </c>
@@ -30203,7 +30203,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>109</v>
       </c>
@@ -30232,7 +30232,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>109</v>
       </c>
@@ -30261,7 +30261,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>110</v>
       </c>
@@ -30290,7 +30290,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>110</v>
       </c>
@@ -30319,7 +30319,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>110</v>
       </c>
@@ -30348,7 +30348,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>111</v>
       </c>
@@ -30377,7 +30377,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>111</v>
       </c>
@@ -30406,7 +30406,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>111</v>
       </c>
@@ -30435,7 +30435,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>112</v>
       </c>
@@ -30464,7 +30464,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>112</v>
       </c>
@@ -30493,7 +30493,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>112</v>
       </c>
@@ -30522,7 +30522,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>113</v>
       </c>
@@ -30551,7 +30551,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>113</v>
       </c>
@@ -30580,7 +30580,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>113</v>
       </c>
@@ -30609,7 +30609,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>114</v>
       </c>
@@ -30638,7 +30638,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>114</v>
       </c>
@@ -30667,7 +30667,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>114</v>
       </c>
@@ -30696,7 +30696,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>115</v>
       </c>
@@ -30725,7 +30725,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>115</v>
       </c>
@@ -30754,7 +30754,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>115</v>
       </c>
@@ -30783,7 +30783,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>116</v>
       </c>
@@ -30812,7 +30812,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>116</v>
       </c>
@@ -30841,7 +30841,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>116</v>
       </c>
@@ -30870,7 +30870,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>117</v>
       </c>
@@ -30899,7 +30899,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>117</v>
       </c>
@@ -30928,7 +30928,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>117</v>
       </c>
@@ -30957,7 +30957,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>118</v>
       </c>
@@ -30986,7 +30986,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>118</v>
       </c>
@@ -31015,7 +31015,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>118</v>
       </c>
@@ -31044,7 +31044,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>119</v>
       </c>
@@ -31073,7 +31073,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>119</v>
       </c>
@@ -31102,7 +31102,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>119</v>
       </c>
@@ -31131,7 +31131,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>120</v>
       </c>
@@ -31160,7 +31160,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>120</v>
       </c>
@@ -31189,7 +31189,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>120</v>
       </c>
@@ -31218,7 +31218,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>121</v>
       </c>
@@ -31247,7 +31247,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>121</v>
       </c>
@@ -31276,7 +31276,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>121</v>
       </c>
@@ -31305,7 +31305,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>135</v>
       </c>
@@ -31334,7 +31334,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>135</v>
       </c>
@@ -31363,7 +31363,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>135</v>
       </c>
@@ -31392,7 +31392,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>122</v>
       </c>
@@ -31421,7 +31421,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>122</v>
       </c>
@@ -31450,7 +31450,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>122</v>
       </c>
@@ -31479,7 +31479,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>123</v>
       </c>
@@ -31508,7 +31508,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>123</v>
       </c>
@@ -31537,7 +31537,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>123</v>
       </c>
@@ -31566,7 +31566,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>124</v>
       </c>
@@ -31595,7 +31595,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>124</v>
       </c>
@@ -31624,7 +31624,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>124</v>
       </c>
@@ -31653,7 +31653,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>125</v>
       </c>
@@ -31682,7 +31682,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>125</v>
       </c>
@@ -31711,7 +31711,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>125</v>
       </c>
@@ -31740,7 +31740,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>126</v>
       </c>
@@ -31769,7 +31769,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>126</v>
       </c>
@@ -31798,7 +31798,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>126</v>
       </c>
@@ -31827,7 +31827,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>127</v>
       </c>
@@ -31856,7 +31856,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>127</v>
       </c>
@@ -31885,7 +31885,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>127</v>
       </c>
@@ -31914,7 +31914,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B304" t="s">
         <v>11</v>
       </c>
@@ -31928,7 +31928,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="305" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B305" t="s">
         <v>11</v>
       </c>
@@ -31942,7 +31942,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="306" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B306" t="s">
         <v>11</v>
       </c>
@@ -31956,7 +31956,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="307" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B307" t="s">
         <v>11</v>
       </c>
@@ -31970,7 +31970,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="308" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B308" t="s">
         <v>11</v>
       </c>
@@ -31984,7 +31984,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="309" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B309" t="s">
         <v>11</v>
       </c>
@@ -31998,7 +31998,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="310" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B310" t="s">
         <v>11</v>
       </c>
@@ -32012,7 +32012,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="311" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B311" t="s">
         <v>11</v>
       </c>
@@ -32026,7 +32026,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="312" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B312" t="s">
         <v>11</v>
       </c>
@@ -32040,7 +32040,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="313" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B313" t="s">
         <v>11</v>
       </c>
@@ -32054,7 +32054,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="314" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B314" t="s">
         <v>11</v>
       </c>
@@ -32068,7 +32068,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="315" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B315" t="s">
         <v>11</v>
       </c>
@@ -32082,7 +32082,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="316" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B316" t="s">
         <v>11</v>
       </c>
@@ -32096,7 +32096,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="317" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B317" t="s">
         <v>11</v>
       </c>
@@ -32110,7 +32110,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="318" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B318" t="s">
         <v>11</v>
       </c>
